--- a/docs/Defect_Tracker Template_v0.1 (1).xlsx
+++ b/docs/Defect_Tracker Template_v0.1 (1).xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
   <si>
     <t>Sl No</t>
   </si>
@@ -122,6 +122,63 @@
   </si>
   <si>
     <t>Generated uploads and knowledge-base files could be added to Git repository.</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>DOCX milestone tables were not extracted by the document loader, causing milestone information to be missing from the agent context.</t>
+  </si>
+  <si>
+    <t>Data Extraction</t>
+  </si>
+  <si>
+    <t>Updated DOCX loader to extract both paragraphs and table contents.</t>
+  </si>
+  <si>
+    <t>Verified with project plan containing milestone table.</t>
+  </si>
+  <si>
+    <t>Scope Extraction Agent returned an empty responsibilities list even when responsibility information was present in the retrieved context.</t>
+  </si>
+  <si>
+    <t>Updated scope extraction prompt and tested responsibility extraction with project documents.</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Requires additional validation with multiple documents.</t>
+  </si>
+  <si>
+    <t>Blocker Agent incorrectly classified the final project deadline as a pending decision.</t>
+  </si>
+  <si>
+    <t>Strengthened pending-decision rules to accept only explicitly unresolved decisions.</t>
+  </si>
+  <si>
+    <t>Further testing required to prevent incorrect classification.</t>
+  </si>
+  <si>
+    <t>Blocker Agent inferred a due date for an action item from a milestone date instead of using an explicitly stated action-item due date.</t>
+  </si>
+  <si>
+    <t>Updated agent instructions to avoid inventing or inferring action-item due dates.</t>
+  </si>
+  <si>
+    <t>Validate using meeting-notes documents.</t>
+  </si>
+  <si>
+    <t>Local Ollama LLM response generation was significantly slower than the previously used OpenAI API.</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Migrated LLM execution from OpenAI API to local Ollama after API credits were exhausted. Performance optimization is pending.</t>
+  </si>
+  <si>
+    <t>Local model provides usable responses but requires optimization.</t>
   </si>
 </sst>
 </file>
@@ -781,69 +838,179 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="6"/>
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="6"/>
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="6"/>
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
@@ -1025,15 +1192,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F50FC49184C87E449886FB52439922C9" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f85b7e58c3d8889ba0673e7b34a193a6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b67b99c0-208c-4860-83e0-51466af787c4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d43477c1ade21a66d9a75ba2d5aa042" ns2:_="">
     <xsd:import namespace="b67b99c0-208c-4860-83e0-51466af787c4"/>
@@ -1165,6 +1323,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
   <ds:schemaRefs>
@@ -1175,14 +1342,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191CB444-B9BF-4C91-94BD-600524521497}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1198,4 +1357,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/Defect_Tracker Template_v0.1 (1).xlsx
+++ b/docs/Defect_Tracker Template_v0.1 (1).xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SIRISRI\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Project-Intelligence-Risk-Advisor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2364" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Defects" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
   <si>
     <t>Sl No</t>
   </si>
@@ -145,9 +145,6 @@
     <t>Updated scope extraction prompt and tested responsibility extraction with project documents.</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
     <t>Requires additional validation with multiple documents.</t>
   </si>
   <si>
@@ -179,6 +176,81 @@
   </si>
   <si>
     <t>Local model provides usable responses but requires optimization.</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>Agent routing returned an incorrect agent for some project queries.</t>
+  </si>
+  <si>
+    <t>Updated routing rules to improve query classification.</t>
+  </si>
+  <si>
+    <t>Verified with scope, risk and blocker queries.</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>Conversational assistant did not retain context for follow-up questions.</t>
+  </si>
+  <si>
+    <t>Added conversation context handling for follow-up queries.</t>
+  </si>
+  <si>
+    <t>Tested with multiple related questions.</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>React frontend did not display backend error responses clearly.</t>
+  </si>
+  <si>
+    <t>Added frontend error handling and user-friendly error messages.</t>
+  </si>
+  <si>
+    <t>Verified API failure handling.</t>
+  </si>
+  <si>
+    <t>24/09/2026</t>
+  </si>
+  <si>
+    <t>Multiple document queries returned incomplete retrieved context.</t>
+  </si>
+  <si>
+    <t>Data Retrieval</t>
+  </si>
+  <si>
+    <t>Improved multi-document retrieval and context handling.</t>
+  </si>
+  <si>
+    <t>Verified using multiple project documents.</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>Conversational assistant generated unsupported responses for unavailable information.</t>
+  </si>
+  <si>
+    <t>Strengthened source-grounding and unavailable-information handling.</t>
+  </si>
+  <si>
+    <t>Verified with questions outside project context.</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t>27/09/2026</t>
+  </si>
+  <si>
+    <t>26/09/2026</t>
   </si>
 </sst>
 </file>
@@ -837,7 +909,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -872,7 +944,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -901,13 +973,13 @@
         <v>34</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -918,7 +990,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3">
         <v>2</v>
@@ -930,19 +1002,19 @@
         <v>9</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -953,7 +1025,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3">
         <v>2</v>
@@ -965,19 +1037,19 @@
         <v>9</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -988,7 +1060,7 @@
         <v>34</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3">
         <v>2</v>
@@ -997,85 +1069,195 @@
         <v>16</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="K11" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="6"/>
+      <c r="D12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
@@ -1186,9 +1368,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1324,19 +1509,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1360,9 +1541,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/Defect_Tracker Template_v0.1 (1).xlsx
+++ b/docs/Defect_Tracker Template_v0.1 (1).xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="75">
   <si>
     <t>Sl No</t>
   </si>
@@ -178,9 +178,6 @@
     <t>Local model provides usable responses but requires optimization.</t>
   </si>
   <si>
-    <t>21/09/2026</t>
-  </si>
-  <si>
     <t>Agent routing returned an incorrect agent for some project queries.</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
   </si>
   <si>
     <t>Verified with scope, risk and blocker queries.</t>
-  </si>
-  <si>
-    <t>22/09/2026</t>
   </si>
   <si>
     <t>Conversational assistant did not retain context for follow-up questions.</t>
@@ -973,7 +967,7 @@
         <v>34</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>41</v>
@@ -1008,7 +1002,7 @@
         <v>34</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>44</v>
@@ -1043,7 +1037,7 @@
         <v>34</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>47</v>
@@ -1078,7 +1072,7 @@
         <v>34</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>51</v>
@@ -1092,10 +1086,10 @@
         <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E12" s="3">
         <v>3</v>
@@ -1107,16 +1101,16 @@
         <v>9</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
@@ -1127,10 +1121,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" s="3">
         <v>3</v>
@@ -1142,16 +1136,16 @@
         <v>9</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
@@ -1162,10 +1156,10 @@
         <v>16</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3">
         <v>3</v>
@@ -1177,16 +1171,16 @@
         <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
@@ -1197,10 +1191,10 @@
         <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3">
         <v>3</v>
@@ -1209,19 +1203,19 @@
         <v>16</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
@@ -1232,10 +1226,10 @@
         <v>16</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3">
         <v>3</v>
@@ -1247,16 +1241,16 @@
         <v>9</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -1368,12 +1362,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1509,15 +1500,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1541,10 +1536,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>